--- a/data/trans_orig/IP28-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP28-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17349</t>
+          <t>16802</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15746</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>14574</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>28923</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104715</t>
+          <t>104357</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119322</t>
+          <t>119302</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>119598</t>
+          <t>118886</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134714</t>
+          <t>134619</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>228843</t>
+          <t>230110</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>249892</t>
+          <t>250110</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,72%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18649</t>
+          <t>18277</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>18627</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17165</t>
+          <t>17616</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33643</t>
+          <t>32681</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>764</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>15703</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21956</t>
+          <t>22195</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19339</t>
+          <t>18440</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34765</t>
+          <t>34415</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>154039</t>
+          <t>154577</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>170058</t>
+          <t>170091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>161492</t>
+          <t>160330</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178925</t>
+          <t>178855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>321823</t>
+          <t>321115</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>344772</t>
+          <t>344153</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,73%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11508</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23811</t>
+          <t>23738</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13010</t>
+          <t>12805</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26040</t>
+          <t>26176</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28266</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44907</t>
+          <t>45592</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11922</t>
+          <t>11313</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>16524</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>21605</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19372</t>
+          <t>19165</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34209</t>
+          <t>33729</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104535</t>
+          <t>104118</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>118029</t>
+          <t>117695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>109459</t>
+          <t>110269</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>125988</t>
+          <t>125943</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>219009</t>
+          <t>220393</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>239450</t>
+          <t>240563</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17640</t>
+          <t>17867</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19538</t>
+          <t>19670</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>18604</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33158</t>
+          <t>32908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7844</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20905</t>
+          <t>21164</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17665</t>
+          <t>17768</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34411</t>
+          <t>35001</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>168993</t>
+          <t>169168</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>184959</t>
+          <t>185085</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>169254</t>
+          <t>170863</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>185291</t>
+          <t>186031</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>343855</t>
+          <t>343232</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>367537</t>
+          <t>366874</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,17%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>7797</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19846</t>
+          <t>20082</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18978</t>
+          <t>18792</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18610</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33416</t>
+          <t>34635</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32674</t>
+          <t>33044</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54564</t>
+          <t>53773</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43822</t>
+          <t>44446</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>67417</t>
+          <t>68344</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>83690</t>
+          <t>82871</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>114910</t>
+          <t>114159</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>549248</t>
+          <t>550624</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>580406</t>
+          <t>580529</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>578842</t>
+          <t>578478</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>610793</t>
+          <t>611044</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1137468</t>
+          <t>1139459</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1180860</t>
+          <t>1182272</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,29%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43328</t>
+          <t>42521</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>65220</t>
+          <t>64441</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46351</t>
+          <t>45948</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>68799</t>
+          <t>69183</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>95083</t>
+          <t>95851</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>127917</t>
+          <t>126855</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>14519</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>14795</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>11499</t>
+          <t>11918</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>25424</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>14411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6165</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>15988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12487</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>26756</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87978</t>
+          <t>88830</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104443</t>
+          <t>104869</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104490</t>
+          <t>105988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121216</t>
+          <t>121935</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>200139</t>
+          <t>198812</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>222109</t>
+          <t>221372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,91%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24109</t>
+          <t>23569</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>21036</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22307</t>
+          <t>22162</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39947</t>
+          <t>39445</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>737</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>723</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11070</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>15411</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12166</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25221</t>
+          <t>24765</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19477</t>
+          <t>19738</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36157</t>
+          <t>36368</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>140673</t>
+          <t>140534</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156510</t>
+          <t>156455</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155322</t>
+          <t>154995</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>173580</t>
+          <t>173197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>301369</t>
+          <t>300206</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>326236</t>
+          <t>325405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16522</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31015</t>
+          <t>31010</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24328</t>
+          <t>24644</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32039</t>
+          <t>31643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50775</t>
+          <t>50248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21278</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16238</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17244</t>
+          <t>17776</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32158</t>
+          <t>31929</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>108484</t>
+          <t>108859</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>122679</t>
+          <t>123249</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>117959</t>
+          <t>117229</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>132847</t>
+          <t>132437</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>232212</t>
+          <t>231671</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>252701</t>
+          <t>252469</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15276</t>
+          <t>15341</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21420</t>
+          <t>21810</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17787</t>
+          <t>17605</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32389</t>
+          <t>32268</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18699</t>
+          <t>18165</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18602</t>
+          <t>18446</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35302</t>
+          <t>34940</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>142807</t>
+          <t>143123</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>162639</t>
+          <t>163417</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>149417</t>
+          <t>149284</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>166737</t>
+          <t>166763</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>298489</t>
+          <t>298112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>324979</t>
+          <t>325171</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,76%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>16370</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31280</t>
+          <t>32155</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10468</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23611</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>29283</t>
+          <t>29131</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>49724</t>
+          <t>50147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>13441</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17009</t>
+          <t>17712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34291</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53471</t>
+          <t>55919</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42196</t>
+          <t>40207</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64227</t>
+          <t>63881</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>80736</t>
+          <t>80976</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>110641</t>
+          <t>111994</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>500896</t>
+          <t>501246</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>534753</t>
+          <t>533769</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>543220</t>
+          <t>547391</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>579138</t>
+          <t>581001</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1057299</t>
+          <t>1057769</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1104055</t>
+          <t>1103945</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,65%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59177</t>
+          <t>59607</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>87172</t>
+          <t>87324</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>50645</t>
+          <t>50209</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75891</t>
+          <t>74822</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>115986</t>
+          <t>117582</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>152654</t>
+          <t>153048</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>17071</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>33627</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>14619</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105190</t>
+          <t>105092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115027</t>
+          <t>115116</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103348</t>
+          <t>103072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117363</t>
+          <t>117037</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>212006</t>
+          <t>212870</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>229856</t>
+          <t>230674</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>19566</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25826</t>
+          <t>25248</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15720</t>
+          <t>16259</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>24221</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156054</t>
+          <t>155429</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>169765</t>
+          <t>169402</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165653</t>
+          <t>166494</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>180062</t>
+          <t>180710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>325734</t>
+          <t>325965</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>346146</t>
+          <t>347264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,01%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19382</t>
+          <t>19904</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15996</t>
+          <t>16273</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>16729</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32000</t>
+          <t>32034</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>572</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13252</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19106</t>
+          <t>19232</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>14243</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27517</t>
+          <t>28269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>112814</t>
+          <t>112966</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>126287</t>
+          <t>126566</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>121622</t>
+          <t>121282</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>137026</t>
+          <t>136766</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>238354</t>
+          <t>238616</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>258964</t>
+          <t>259112</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19525</t>
+          <t>19440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>17723</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>18705</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33524</t>
+          <t>34821</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18323</t>
+          <t>18387</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25742</t>
+          <t>25582</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153507</t>
+          <t>153756</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>168271</t>
+          <t>168253</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>151149</t>
+          <t>151237</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>167321</t>
+          <t>167726</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>310344</t>
+          <t>310759</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>331917</t>
+          <t>332718</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20254</t>
+          <t>20654</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20868</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17825</t>
+          <t>18184</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>35147</t>
+          <t>34749</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>701</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17331</t>
+          <t>17697</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32808</t>
+          <t>32592</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30183</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50537</t>
+          <t>50011</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>52051</t>
+          <t>50880</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>78626</t>
+          <t>77021</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>543558</t>
+          <t>543039</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>568704</t>
+          <t>568829</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>559076</t>
+          <t>558800</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>588912</t>
+          <t>589545</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1110906</t>
+          <t>1109985</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1149891</t>
+          <t>1150956</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37503</t>
+          <t>36429</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57350</t>
+          <t>57137</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36674</t>
+          <t>36128</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58248</t>
+          <t>59487</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>77666</t>
+          <t>79374</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108343</t>
+          <t>110206</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30734</t>
+          <t>32407</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42539</t>
+          <t>39182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91351</t>
+          <t>90872</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103805</t>
+          <t>103953</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97459</t>
+          <t>97510</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123711</t>
+          <t>124783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>191709</t>
+          <t>196408</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>223151</t>
+          <t>223518</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13233</t>
+          <t>12611</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20265</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14157</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30639</t>
+          <t>30193</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>503</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14298</t>
+          <t>15211</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>12911</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28037</t>
+          <t>28306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19890</t>
+          <t>20104</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37542</t>
+          <t>38849</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>159776</t>
+          <t>159303</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>175444</t>
+          <t>174747</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204724</t>
+          <t>204235</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>225466</t>
+          <t>225037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>370666</t>
+          <t>371266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>397352</t>
+          <t>398062</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20367</t>
+          <t>19565</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>24615</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18907</t>
+          <t>18598</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37935</t>
+          <t>37539</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>706</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>694</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14646</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36317</t>
+          <t>36481</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>13138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28807</t>
+          <t>29012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31633</t>
+          <t>31422</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58701</t>
+          <t>59425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>137536</t>
+          <t>137302</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>166000</t>
+          <t>166591</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>130458</t>
+          <t>129790</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>155593</t>
+          <t>154209</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>274669</t>
+          <t>277399</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>314698</t>
+          <t>315359</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,31%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16685</t>
+          <t>17099</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>10338</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32415</t>
+          <t>33253</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18085</t>
+          <t>18321</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44876</t>
+          <t>43893</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>489</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>10031</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22328</t>
+          <t>23077</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11783</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26834</t>
+          <t>27201</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25281</t>
+          <t>24765</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44984</t>
+          <t>44638</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125805</t>
+          <t>124928</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>143003</t>
+          <t>142534</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>138975</t>
+          <t>138798</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156762</t>
+          <t>157708</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>270603</t>
+          <t>270107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>296119</t>
+          <t>296013</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>20464</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18731</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18164</t>
+          <t>18012</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>34903</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>825</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12065,42 +12065,42 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>4191</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>9801</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>2,82%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>4191</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1584</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>9779</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>45478</t>
+          <t>44761</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>73197</t>
+          <t>72193</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54652</t>
+          <t>54868</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>90386</t>
+          <t>90894</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>109578</t>
+          <t>107332</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>155151</t>
+          <t>153524</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>533826</t>
+          <t>533098</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>571121</t>
+          <t>570763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>601400</t>
+          <t>597744</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>646419</t>
+          <t>645724</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1143178</t>
+          <t>1143279</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1202516</t>
+          <t>1204464</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31091</t>
+          <t>33273</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55606</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>43742</t>
+          <t>44650</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>74933</t>
+          <t>75901</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>82574</t>
+          <t>83015</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>121320</t>
+          <t>121802</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17119</t>
+          <t>16868</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>25992</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
